--- a/artfynd/A 31216-2026 artfynd.xlsx
+++ b/artfynd/A 31216-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,9 +790,260 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135751965</v>
+      </c>
+      <c r="B3" t="n">
+        <v>9415</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>fragment</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kastkärr, Stensnäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>581817</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6437376</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skogsbilvägen</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Sven Halling, Ann Newsome</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751965</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135751809</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99252</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stensnäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>581613</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6437401</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vägkante, norra sidan</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751809</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31216-2026 artfynd.xlsx
+++ b/artfynd/A 31216-2026 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>135751809</v>
       </c>
       <c r="B4" t="n">
-        <v>99252</v>
+        <v>99254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31216-2026 artfynd.xlsx
+++ b/artfynd/A 31216-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135751965</v>
       </c>
       <c r="B3" t="n">
-        <v>9415</v>
+        <v>9417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135751809</v>
       </c>
       <c r="B4" t="n">
-        <v>99254</v>
+        <v>99271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31216-2026 artfynd.xlsx
+++ b/artfynd/A 31216-2026 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>135751809</v>
       </c>
       <c r="B4" t="n">
-        <v>99271</v>
+        <v>99272</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31216-2026 artfynd.xlsx
+++ b/artfynd/A 31216-2026 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>135751809</v>
       </c>
       <c r="B4" t="n">
-        <v>99272</v>
+        <v>99273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31216-2026 artfynd.xlsx
+++ b/artfynd/A 31216-2026 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>135751809</v>
       </c>
       <c r="B4" t="n">
-        <v>99273</v>
+        <v>99274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31216-2026 artfynd.xlsx
+++ b/artfynd/A 31216-2026 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>135751809</v>
       </c>
       <c r="B4" t="n">
-        <v>99274</v>
+        <v>99280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31216-2026 artfynd.xlsx
+++ b/artfynd/A 31216-2026 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>135751809</v>
       </c>
       <c r="B4" t="n">
-        <v>99280</v>
+        <v>99281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
